--- a/CSC-580-Advanced-Software-Engineering/Books/Zachman Framework Template for Breakout, Homework, and Exams.xlsx
+++ b/CSC-580-Advanced-Software-Engineering/Books/Zachman Framework Template for Breakout, Homework, and Exams.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhart\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe89f82f9193bbdc/Documents/GitHub/ai-masters-workspace/CSC-580-Advanced-Software-Engineering/Books/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74264736-520B-4D47-9619-AFA7CF464DD7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74264736-520B-4D47-9619-AFA7CF464DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="1545" windowWidth="28800" windowHeight="18450" xr2:uid="{A35AE857-94A8-4C17-9DF0-7CB4E23FB22B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A35AE857-94A8-4C17-9DF0-7CB4E23FB22B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -94,11 +94,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1" rgb="000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,9 +163,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,7 +203,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -310,7 +309,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -452,7 +451,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,9 +462,9 @@
   <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="19.140625"/>
-    <col min="2" max="2" customWidth="true" width="1.85546875"/>
-    <col min="3" max="3" customWidth="true" width="50.140625"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="1.85546875" customWidth="1"/>
+    <col min="3" max="3" width="50.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -824,7 +823,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C2:C11 C14:C23 C26:C35 C38:C47 C50:C59 C62:C71" numberStoredAsText="1"/>
+    <ignoredError sqref="C4:C11 C14:C23 C26:C35 C38:C47 C50:C59 C62:C71" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>